--- a/i_test/test_D4_pop_ASL/D3_ASL.xlsx
+++ b/i_test/test_D4_pop_ASL/D3_ASL.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="6">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8" uniqueCount="7">
   <si>
     <t xml:space="preserve">person_id</t>
   </si>
@@ -32,6 +32,9 @@
   </si>
   <si>
     <t xml:space="preserve">ASL</t>
+  </si>
+  <si>
+    <t xml:space="preserve">birth_date</t>
   </si>
   <si>
     <t xml:space="preserve">CE</t>
@@ -113,8 +116,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -135,54 +142,66 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:E4"/>
   <sheetFormatPr defaultColWidth="8.453125" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
     <row r="1" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="0" t="s">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="0" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="0" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="0" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
+      <c r="E1" s="0" t="s">
+        <v>4</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B2" s="0" t="n">
+      <c r="B2" s="1" t="n">
         <v>20130101</v>
       </c>
-      <c r="C2" s="0" t="n">
+      <c r="C2" s="1" t="n">
         <v>20261231</v>
       </c>
-      <c r="D2" s="0" t="s">
-        <v>4</v>
+      <c r="D2" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E2" s="0" t="n">
+        <v>19981231</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B3" s="0" t="n">
+      <c r="B3" s="1" t="n">
         <v>20160101</v>
       </c>
-      <c r="C3" s="0" t="n">
+      <c r="C3" s="1" t="n">
         <v>20181231</v>
       </c>
-      <c r="D3" s="0" t="s">
-        <v>4</v>
+      <c r="D3" s="1" t="s">
+        <v>5</v>
+      </c>
+      <c r="E3" s="0" t="n">
+        <v>19700101</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="B4" s="0" t="n">
+      <c r="B4" s="1" t="n">
         <v>20130101</v>
       </c>
-      <c r="C4" s="0" t="n">
+      <c r="C4" s="1" t="n">
         <v>20261231</v>
       </c>
-      <c r="D4" s="0" t="s">
-        <v>5</v>
+      <c r="D4" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="E4" s="0" t="n">
+        <v>19990101</v>
       </c>
     </row>
   </sheetData>
